--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcBill.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcBill.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="质检日报" sheetId="1" r:id="rId1"/>
@@ -62,13 +62,13 @@
     <t>质检员</t>
   </si>
   <si>
-    <t>质检数量</t>
-  </si>
-  <si>
-    <t>不良品数量</t>
-  </si>
-  <si>
-    <t>抽检不良率</t>
+    <t>抽检数量</t>
+  </si>
+  <si>
+    <t>抽检不良品数量</t>
+  </si>
+  <si>
+    <t>抽检不合格率</t>
   </si>
   <si>
     <t>问题属性</t>
@@ -195,7 +195,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -207,6 +207,12 @@
       <b/>
       <sz val="13"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -681,156 +687,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1416,13 +1425,13 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
